--- a/en/downloads/data-excel/15.1.2.1.xlsx
+++ b/en/downloads/data-excel/15.1.2.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98796736-CC9D-4FB4-B2B4-30C069892CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -70,11 +71,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +140,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -178,13 +186,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -219,18 +228,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Normal 17" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+  <cellStyles count="5">
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7 2" xfId="2"/>
+    <cellStyle name="Обычный 6" xfId="4" xr:uid="{3AFF9444-E8EF-42B5-A484-BEC7911B082B}"/>
+    <cellStyle name="Обычный 7 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -507,7 +521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
@@ -516,7 +530,7 @@
     <col min="6" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -529,18 +543,18 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:15" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -552,8 +566,9 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
+      <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
@@ -599,8 +614,11 @@
       <c r="O4" s="4">
         <v>2023</v>
       </c>
+      <c r="P4" s="15">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
@@ -645,6 +663,9 @@
       </c>
       <c r="O5" s="5">
         <v>6.53</v>
+      </c>
+      <c r="P5" s="13">
+        <v>6.92</v>
       </c>
     </row>
     <row r="21" spans="13:16" x14ac:dyDescent="0.25">
